--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.56576688340675</v>
+        <v>3.504437118553597</v>
       </c>
       <c r="D2" t="n">
-        <v>17.01881311960384</v>
+        <v>2.765557131935625</v>
       </c>
       <c r="E2" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F2" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.70772235813319</v>
+        <v>3.040004883196644</v>
       </c>
       <c r="D3" t="n">
-        <v>19.9706462125752</v>
+        <v>3.245230009543471</v>
       </c>
       <c r="E3" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F3" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.12057943316412</v>
+        <v>4.407094157889169</v>
       </c>
       <c r="D4" t="n">
-        <v>19.33278800987176</v>
+        <v>3.141578051604161</v>
       </c>
       <c r="E4" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F4" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.0386173980534</v>
+        <v>2.931275327183677</v>
       </c>
       <c r="D5" t="n">
-        <v>17.48755508319979</v>
+        <v>2.841727701019967</v>
       </c>
       <c r="E5" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F5" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.49375150964533</v>
+        <v>5.767734620317366</v>
       </c>
       <c r="D6" t="n">
-        <v>34.85493003950772</v>
+        <v>5.663926131420005</v>
       </c>
       <c r="E6" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F6" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.18229615910799</v>
+        <v>3.279623125855048</v>
       </c>
       <c r="D7" t="n">
-        <v>20.84639807639242</v>
+        <v>3.387539687413768</v>
       </c>
       <c r="E7" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F7" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.00856402698503</v>
+        <v>5.201391654385068</v>
       </c>
       <c r="D8" t="n">
-        <v>32.74021980325706</v>
+        <v>5.320285718029273</v>
       </c>
       <c r="E8" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F8" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.07519114852633</v>
+        <v>4.562218561635529</v>
       </c>
       <c r="D9" t="n">
-        <v>28.81064570426874</v>
+        <v>4.681729926943671</v>
       </c>
       <c r="E9" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F9" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.84444983044839</v>
+        <v>4.687223097447863</v>
       </c>
       <c r="D10" t="n">
-        <v>28.60835791506148</v>
+        <v>4.64885816119749</v>
       </c>
       <c r="E10" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F10" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.62485740181974</v>
+        <v>3.189039327795708</v>
       </c>
       <c r="D11" t="n">
-        <v>18.13300559229427</v>
+        <v>2.946613408747819</v>
       </c>
       <c r="E11" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F11" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.98452387390828</v>
+        <v>4.709985129510096</v>
       </c>
       <c r="D12" t="n">
-        <v>25.49986569651431</v>
+        <v>4.143728175683576</v>
       </c>
       <c r="E12" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F12" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.446874173025694</v>
+        <v>1.210117053116675</v>
       </c>
       <c r="D13" t="n">
-        <v>5.298262615580052</v>
+        <v>0.8609676750317585</v>
       </c>
       <c r="E13" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F13" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.96075981211438</v>
+        <v>1.781123469468587</v>
       </c>
       <c r="D14" t="n">
-        <v>1.597443418578756</v>
+        <v>0.2595845555190478</v>
       </c>
       <c r="E14" t="n">
-        <v>7.84923149881004</v>
+        <v>1.275500118556631</v>
       </c>
       <c r="F14" t="n">
-        <v>9.329868044230784</v>
+        <v>1.516103557187503</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
